--- a/Vayikra 5787.xlsx
+++ b/Vayikra 5787.xlsx
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -2499,7 +2499,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -2529,7 +2529,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -2544,7 +2544,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -2559,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -2574,7 +2574,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -2589,7 +2589,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -2604,7 +2604,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Metzora&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -3026,7 +3026,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -3041,7 +3041,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3071,7 +3071,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -3086,7 +3086,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach I&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -3508,7 +3508,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -3523,7 +3523,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -3538,7 +3538,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3553,7 +3553,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -3568,7 +3568,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach II&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -3990,7 +3990,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -4005,7 +4005,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -4020,7 +4020,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -4035,7 +4035,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -4050,7 +4050,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -4065,7 +4065,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -4080,7 +4080,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach Shabbat Chol ha-Moed&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -4450,7 +4450,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -4502,7 +4502,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -4517,7 +4517,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -4532,7 +4532,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -4547,7 +4547,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -4562,7 +4562,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VII&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -4969,7 +4969,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -4984,7 +4984,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -4999,7 +4999,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -5014,7 +5014,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -5029,7 +5029,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -5044,7 +5044,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pesach VIII&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -5451,7 +5451,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5466,7 +5466,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -5481,7 +5481,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -5496,7 +5496,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -5511,7 +5511,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -5526,7 +5526,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -5541,7 +5541,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -5556,7 +5556,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Achrei Mot&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -5967,7 +5967,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5982,7 +5982,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -5997,7 +5997,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6012,7 +6012,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -6027,7 +6027,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -6042,7 +6042,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -6057,7 +6057,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -6072,7 +6072,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Kedoshim&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom HaAtzma'ut", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom HaAtzma'ut&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -6479,7 +6479,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom HaAtzma'ut&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom HaAtzma'ut&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -6494,7 +6494,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom HaAtzma'ut&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom HaAtzma'ut&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -6509,7 +6509,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom HaAtzma'ut&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yom HaAtzma'ut&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -6916,7 +6916,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -6931,7 +6931,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -6946,7 +6946,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6961,7 +6961,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -6976,7 +6976,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -6991,7 +6991,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -7006,7 +7006,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -7021,7 +7021,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Emor&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -7447,7 +7447,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -7462,7 +7462,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -7477,7 +7477,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -7492,7 +7492,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -7507,7 +7507,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -7522,7 +7522,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -7537,7 +7537,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayikra&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -7944,7 +7944,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -7959,7 +7959,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -7974,7 +7974,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -7989,7 +7989,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -8004,7 +8004,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -8019,7 +8019,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -8034,7 +8034,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -8049,7 +8049,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Behar&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -8456,7 +8456,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -8471,7 +8471,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -8486,7 +8486,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -8501,7 +8501,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -8516,7 +8516,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -8531,7 +8531,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -8546,7 +8546,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -8561,7 +8561,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bechukotai&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -8968,7 +8968,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -8983,7 +8983,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -8998,7 +8998,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther (Mincha)", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther (Mincha)&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -9401,7 +9401,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther (Mincha)&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther (Mincha)&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -9416,7 +9416,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther (Mincha)&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther (Mincha)&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -9431,7 +9431,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther (Mincha)&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ta'anit Esther (Mincha)&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Purim", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Erev Purim&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Purim", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Purim&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Purim&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Purim&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -10229,7 +10229,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Purim&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Purim&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -10244,7 +10244,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Purim&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Purim&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -10651,7 +10651,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -10666,7 +10666,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -10681,7 +10681,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -10696,7 +10696,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -10711,7 +10711,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -10726,7 +10726,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -10741,7 +10741,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -10756,7 +10756,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tzav&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -11167,7 +11167,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -11182,7 +11182,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -11197,7 +11197,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -11212,7 +11212,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -11227,7 +11227,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -11242,7 +11242,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -11257,7 +11257,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -11272,7 +11272,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shmini&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -11679,7 +11679,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -11694,7 +11694,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -11709,7 +11709,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -11724,7 +11724,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -11739,7 +11739,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -11754,7 +11754,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -11769,7 +11769,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -11784,7 +11784,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tazria&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
